--- a/bomix-app/backend/excel/PROJ_ORDER_EZBOM_EVT_0.1_MatrixBOM_20260807.xlsx
+++ b/bomix-app/backend/excel/PROJ_ORDER_EZBOM_EVT_0.1_MatrixBOM_20260807.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="2712" windowWidth="22152" windowHeight="20400"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="SMD" sheetId="2" r:id="rId1"/>
@@ -126,9 +126,6 @@
     <t>VPORT0402L101V05</t>
   </si>
   <si>
-    <t>AD2,AD3,AD4,AD5,AD6,AD7</t>
-  </si>
-  <si>
     <t>Phase: {{.Phase}}</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -186,6 +183,10 @@
   </si>
   <si>
     <t>{{.ModelQtyG}}</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>AJ1,AU2</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
@@ -414,29 +415,29 @@
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -773,64 +774,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="5"/>
     <col customWidth="true" max="2" min="2" width="14"/>
-    <col customWidth="true" max="3" min="3" width="9.75"/>
+    <col customWidth="true" max="3" min="3" width="9.7109375"/>
     <col customWidth="true" max="4" min="4" width="36"/>
     <col customWidth="true" max="5" min="5" width="15"/>
     <col customWidth="true" max="6" min="6" width="20"/>
     <col customWidth="true" max="7" min="7" width="5"/>
-    <col customWidth="true" max="8" min="8" width="23.25"/>
-    <col bestFit="true" customWidth="true" max="9" min="9" width="6.875"/>
-    <col customWidth="true" max="10" min="10" width="5.625"/>
+    <col customWidth="true" max="8" min="8" width="23.28515625"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="6.85546875"/>
+    <col customWidth="true" max="10" min="10" width="5.5703125"/>
     <col customWidth="true" max="18" min="11" width="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3"/>
@@ -862,7 +863,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="20.4">
+    <row r="4" spans="1:18" ht="22.5">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>51</v>
@@ -902,7 +903,7 @@
       </c>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="20.4">
+    <row r="5" spans="1:18" ht="33.75">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -958,7 +959,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="30.6">
+    <row r="6" spans="1:18" ht="33.75">
       <c r="A6" s="6" t="s">
         <v>57</v>
       </c>
@@ -978,41 +979,41 @@
       <c r="G6" s="6">
         <v>2</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="15" t="str">
+      <c r="H6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="12" t="str">
         <f>=G6*J6</f>
       </c>
-      <c r="J6" s="15" t="str">
+      <c r="J6" s="12" t="str">
         <f>IF(EXACT(K6,"V"),K$5,0)+IF(EXACT(L6,"V"),L$5,0)+IF(EXACT(M6,"V"),M$5,0)+IF(EXACT(N6,"V"),N$5,0)+IF(EXACT(O6,"V"),O$5,0)+IF(EXACT(P6,"V"),P$5,0)+IF(EXACT(Q6,"V"),Q$5,0)</f>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="L6" s="17" t="s">
+      <c r="L6" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="20.4">
+      <c r="N6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="22.5">
       <c r="A7" s="7"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -1020,26 +1021,26 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q7" s="16" t="s">
+      <c r="H7" s="18"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="13" t="s">
         <v>19</v>
       </c>
       <c r="R7" s="9" t="s">
@@ -1062,63 +1063,543 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="5"/>
+    <col customWidth="true" max="2" min="2" width="14"/>
+    <col customWidth="true" max="3" min="3" width="9.7109375"/>
+    <col customWidth="true" max="4" min="4" width="36"/>
+    <col customWidth="true" max="5" min="5" width="15"/>
+    <col customWidth="true" max="6" min="6" width="20"/>
+    <col customWidth="true" max="7" min="7" width="5"/>
+    <col customWidth="true" max="8" min="8" width="23.28515625"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="6.85546875"/>
+    <col customWidth="true" max="10" min="10" width="5.5703125"/>
+    <col customWidth="true" max="18" min="11" width="6"/>
+  </cols>
   <sheetData>
-    <row r="5">
-      <c r="K5">
+    <row r="1" spans="1:18">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" ht="22.5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="1:18" ht="33.75">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L5">
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M5">
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2">
+        <v>5</v>
+      </c>
+      <c r="M5" s="2">
         <v>7</v>
       </c>
-      <c r="N5" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>19</v>
-      </c>
+      <c r="N5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="33.75">
+      <c r="A6" s="6"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="22.5">
+      <c r="A7" s="7"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+  </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="5"/>
+    <col customWidth="true" max="2" min="2" width="14"/>
+    <col customWidth="true" max="3" min="3" width="9.7109375"/>
+    <col customWidth="true" max="4" min="4" width="36"/>
+    <col customWidth="true" max="5" min="5" width="15"/>
+    <col customWidth="true" max="6" min="6" width="20"/>
+    <col customWidth="true" max="7" min="7" width="5"/>
+    <col customWidth="true" max="8" min="8" width="23.28515625"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="6.85546875"/>
+    <col customWidth="true" max="10" min="10" width="5.5703125"/>
+    <col customWidth="true" max="18" min="11" width="6"/>
+  </cols>
   <sheetData>
-    <row r="5">
-      <c r="K5">
+    <row r="1" spans="1:18">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" ht="22.5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="1:18" ht="33.75">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L5">
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M5">
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2">
+        <v>5</v>
+      </c>
+      <c r="M5" s="2">
         <v>7</v>
       </c>
-      <c r="N5" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>19</v>
-      </c>
+      <c r="N5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="33.75">
+      <c r="A6" s="6"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="22.5">
+      <c r="A7" s="7"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+  </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>